--- a/南宁通信段劳动用工工时、工分统计表工区.xlsx
+++ b/南宁通信段劳动用工工时、工分统计表工区.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11805"/>
+    <workbookView windowWidth="29868" windowHeight="12935"/>
   </bookViews>
   <sheets>
     <sheet name="A工区" sheetId="19" r:id="rId1"/>
@@ -743,12 +743,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1962,12 +1962,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:DJ69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
-    <col min="2" max="3" width="10.875" style="2" customWidth="1"/>
-    <col min="4" max="112" width="7.625" style="2" customWidth="1"/>
-    <col min="113" max="113" width="7.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.8796296296296" style="2" customWidth="1"/>
+    <col min="2" max="3" width="10.8796296296296" style="2" customWidth="1"/>
+    <col min="4" max="112" width="7.62962962962963" style="2" customWidth="1"/>
+    <col min="113" max="113" width="7.62962962962963" style="1" customWidth="1"/>
     <col min="114" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5785,10 +5785,7 @@
       <c r="DE28" s="44"/>
       <c r="DF28" s="44"/>
       <c r="DG28" s="44"/>
-      <c r="DH28" s="26">
-        <f>D28+E28+F28+H28+I28+J28+L28+M28+N28+P28+Q28+R28+T28+U28+V28+X28+Y28+Z28+AB28+AC28+AD28+AF28+AG28+AH28+AJ28+AK28+AL28+AM28+AN28+AO28+AP28+AQ28+AS28+AT28+AU28+AV28+AW28+AX28+AY28+AZ28+BA28+BB28+BC28+BD28+BE28+BF28+BG28+BH28+BI28+BJ28+BL28+BM28+BN28+BO28+BP28+BQ28+BS28+BT28+BU28+BV28+BW28+BX28+BY28+BZ28+CB28+CD28+CF28+CH28+CJ28+CL28+CN28+CO28+CP28+CQ28+CR28+CT28+CU28+CW28+CY28+CZ28+DA28+DB28+DC28+DD28+DE28+DF28+DG28</f>
-        <v>0</v>
-      </c>
+      <c r="DH28" s="26"/>
       <c r="DI28" s="47"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="15" customHeight="1" spans="1:114">
@@ -5905,10 +5902,7 @@
       <c r="DE29" s="44"/>
       <c r="DF29" s="44"/>
       <c r="DG29" s="44"/>
-      <c r="DH29" s="26">
-        <f>D29+E29+F29+H29+I29+J29+L29+M29+N29+P29+Q29+R29+T29+U29+V29+X29+Y29+Z29+AB29+AC29+AD29+AF29+AG29+AH29+AJ29+AK29+AL29+AM29+AN29+AO29+AP29+AQ29+AS29+AT29+AU29+AV29+AW29+AX29+AY29+AZ29+BA29+BB29+BC29+BD29+BE29+BF29+BG29+BH29+BI29+BJ29+BL29+BM29+BN29+BO29+BP29+BQ29+BS29+BT29+BU29+BV29+BW29+BX29+BY29+BZ29+CB29+CD29+CF29+CH29+CJ29+CL29+CN29+CO29+CP29+CQ29+CR29+CT29+CU29+CW29+CY29+CZ29+DA29+DB29+DC29+DD29+DE29+DF29+DG29</f>
-        <v>0</v>
-      </c>
+      <c r="DH29" s="26"/>
       <c r="DI29" s="47"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="15" customHeight="1" spans="1:114">
@@ -6029,10 +6023,7 @@
       <c r="DE30" s="26"/>
       <c r="DF30" s="26"/>
       <c r="DG30" s="26"/>
-      <c r="DH30" s="26">
-        <f>D30+E30+F30+H30+I30+J30+L30+M30+N30+P30+Q30+R30+T30+U30+V30+X30+Y30+Z30+AB30+AC30+AD30+AF30+AG30+AH30+AJ30+AK30+AL30+AM30+AN30+AO30+AP30+AQ30+AS30+AT30+AU30+AV30+AW30+AX30+AY30+AZ30+BA30+BB30+BC30+BD30+BE30+BF30+BG30+BH30+BI30+BJ30+BL30+BM30+BN30+BO30+BP30+BQ30+BS30+BT30+BU30+BV30+BW30+BX30+BY30+BZ30+CB30+CD30+CF30+CH30+CJ30+CL30+CN30+CO30+CP30+CQ30+CR30+CT30+CU30+CW30+CY30+CZ30+DA30+DB30+DC30+DD30+DE30+DF30+DG30</f>
-        <v>0</v>
-      </c>
+      <c r="DH30" s="26"/>
       <c r="DI30" s="39"/>
       <c r="DJ30" s="40"/>
     </row>
@@ -6150,10 +6141,7 @@
       <c r="DE31" s="26"/>
       <c r="DF31" s="26"/>
       <c r="DG31" s="26"/>
-      <c r="DH31" s="26">
-        <f>D31+E31+F31+H31+I31+J31+L31+M31+N31+P31+Q31+R31+T31+U31+V31+X31+Y31+Z31+AB31+AC31+AD31+AF31+AG31+AH31+AJ31+AK31+AL31+AM31+AN31+AO31+AP31+AQ31+AS31+AT31+AU31+AV31+AW31+AX31+AY31+AZ31+BA31+BB31+BC31+BD31+BE31+BF31+BG31+BH31+BI31+BJ31+BL31+BM31+BN31+BO31+BP31+BQ31+BS31+BT31+BU31+BV31+BW31+BX31+BY31+BZ31+CB31+CD31+CF31+CH31+CJ31+CL31+CN31+CO31+CP31+CQ31+CR31+CT31+CU31+CW31+CY31+CZ31+DA31+DB31+DC31+DD31+DE31+DF31+DG31</f>
-        <v>0</v>
-      </c>
+      <c r="DH31" s="26"/>
       <c r="DI31" s="39"/>
       <c r="DJ31" s="40"/>
     </row>
@@ -6275,10 +6263,7 @@
       <c r="DE32" s="39"/>
       <c r="DF32" s="39"/>
       <c r="DG32" s="39"/>
-      <c r="DH32" s="26">
-        <f>D32+E32+F32+H32+I32+J32+L32+M32+N32+P32+Q32+R32+T32+U32+V32+X32+Y32+Z32+AB32+AC32+AD32+AF32+AG32+AH32+AJ32+AK32+AL32+AM32+AN32+AO32+AP32+AQ32+AS32+AT32+AU32+AV32+AW32+AX32+AY32+AZ32+BA32+BB32+BC32+BD32+BE32+BF32+BG32+BH32+BI32+BJ32+BL32+BM32+BN32+BO32+BP32+BQ32+BS32+BT32+BU32+BV32+BW32+BX32+BY32+BZ32+CB32+CD32+CF32+CH32+CJ32+CL32+CN32+CO32+CP32+CQ32+CR32+CT32+CU32+CW32+CY32+CZ32+DA32+DB32+DC32+DD32+DE32+DF32+DG32</f>
-        <v>0</v>
-      </c>
+      <c r="DH32" s="26"/>
       <c r="DI32" s="39"/>
       <c r="DJ32" s="40"/>
     </row>
@@ -6396,10 +6381,7 @@
       <c r="DE33" s="39"/>
       <c r="DF33" s="39"/>
       <c r="DG33" s="39"/>
-      <c r="DH33" s="26">
-        <f>D33+E33+F33+H33+I33+J33+L33+M33+N33+P33+Q33+R33+T33+U33+V33+X33+Y33+Z33+AB33+AC33+AD33+AF33+AG33+AH33+AJ33+AK33+AL33+AM33+AN33+AO33+AP33+AQ33+AS33+AT33+AU33+AV33+AW33+AX33+AY33+AZ33+BA33+BB33+BC33+BD33+BE33+BF33+BG33+BH33+BI33+BJ33+BL33+BM33+BN33+BO33+BP33+BQ33+BS33+BT33+BU33+BV33+BW33+BX33+BY33+BZ33+CB33+CD33+CF33+CH33+CJ33+CL33+CN33+CO33+CP33+CQ33+CR33+CT33+CU33+CW33+CY33+CZ33+DA33+DB33+DC33+DD33+DE33+DF33+DG33</f>
-        <v>0</v>
-      </c>
+      <c r="DH33" s="26"/>
       <c r="DI33" s="39"/>
       <c r="DJ33" s="40"/>
     </row>
@@ -6521,10 +6503,7 @@
       <c r="DE34" s="39"/>
       <c r="DF34" s="39"/>
       <c r="DG34" s="39"/>
-      <c r="DH34" s="26">
-        <f>D34+E34+F34+H34+I34+J34+L34+M34+N34+P34+Q34+R34+T34+U34+V34+X34+Y34+Z34+AB34+AC34+AD34+AF34+AG34+AH34+AJ34+AK34+AL34+AM34+AN34+AO34+AP34+AQ34+AS34+AT34+AU34+AV34+AW34+AX34+AY34+AZ34+BA34+BB34+BC34+BD34+BE34+BF34+BG34+BH34+BI34+BJ34+BL34+BM34+BN34+BO34+BP34+BQ34+BS34+BT34+BU34+BV34+BW34+BX34+BY34+BZ34+CB34+CD34+CF34+CH34+CJ34+CL34+CN34+CO34+CP34+CQ34+CR34+CT34+CU34+CW34+CY34+CZ34+DA34+DB34+DC34+DD34+DE34+DF34+DG34</f>
-        <v>0</v>
-      </c>
+      <c r="DH34" s="26"/>
       <c r="DI34" s="39"/>
       <c r="DJ34" s="40"/>
     </row>
